--- a/data/merged/2026-09-23/MERGED_US_Wet-Dry-Floor-Washer_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_US_Wet-Dry-Floor-Washer_2026-09-23.xlsx
@@ -3345,7 +3345,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3389,7 +3389,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3471,13 +3471,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3515,13 +3515,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3697,7 +3697,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3741,7 +3741,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3779,13 +3779,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3867,13 +3867,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3999,13 +3999,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4043,7 +4043,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4087,7 +4087,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4219,13 +4219,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4307,13 +4307,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4351,13 +4351,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4615,13 +4615,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4659,13 +4659,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5187,13 +5187,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5319,13 +5319,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5407,13 +5407,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5430,94 +5430,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5859,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6274,7 +6186,7 @@
       <c r="B2" s="13"/>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>B003R3JFJO</t>
+          <t>B079WCPPQD</t>
         </is>
       </c>
       <c r="D2" s="14"/>
@@ -6287,23 +6199,23 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>Bissell Garage Pro Wall-Mounted Wet Dry Vacuum/Blower, 18P03sAuto tool kit included; wall-mount saves floor space; wet/dry</t>
+          <t>Bissell CrossWave Pet Pro Wet Dry Vacuum Mop, Hard Floors, 2306AsAll-in-one vacuum &amp; mop; area rugs &amp; hard floors; Purple c</t>
         </is>
       </c>
       <c r="I2" s="14"/>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B003R3JFJO?psc=1</t>
+          <t>https://www.amazon.com/dp/B079WCPPQD?psc=1</t>
         </is>
       </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71COfcQjt0L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71THlFoTXFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>B003R3JFJO</t>
+          <t>B079WCPPQD</t>
         </is>
       </c>
       <c r="M2" s="1"/>
@@ -6320,17 +6232,17 @@
       <c r="X2" s="15"/>
       <c r="Y2"/>
       <c r="Z2" s="19">
-        <v>249.99</v>
+        <v>219.99</v>
       </c>
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
       <c r="AD2" s="20">
-        <v>3676</v>
+        <v>25421</v>
       </c>
       <c r="AE2"/>
       <c r="AF2" s="21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG2" s="22">
         <v>0</v>
@@ -6382,7 +6294,7 @@
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>B079WCPPQD</t>
+          <t>B09QFHPPZD</t>
         </is>
       </c>
       <c r="D3" s="14"/>
@@ -6395,23 +6307,23 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>Bissell CrossWave Pet Pro Wet Dry Vacuum Mop, Hard Floors, 2306AsAll-in-one vacuum &amp; mop; area rugs &amp; hard floors; Purple c</t>
+          <t>Tineco Corded Wet Dry Vacuum Steam Mop All-in-one, Hardwood Floor Cleaner Great for Sticky Messes, Floor ONE S5 Steam Smart f</t>
         </is>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B079WCPPQD?psc=1</t>
+          <t>https://www.amazon.com/dp/B09QFHPPZD?psc=1</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71THlFoTXFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61DuH1C9gWL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>B079WCPPQD</t>
+          <t>B09QFHPPZD</t>
         </is>
       </c>
       <c r="M3" s="1"/>
@@ -6428,17 +6340,17 @@
       <c r="X3" s="15"/>
       <c r="Y3"/>
       <c r="Z3" s="19">
-        <v>219.99</v>
+        <v>229</v>
       </c>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3" s="20">
-        <v>25421</v>
+        <v>1377</v>
       </c>
       <c r="AE3"/>
       <c r="AF3" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG3" s="22">
         <v>0</v>
@@ -6490,7 +6402,7 @@
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>B09QFHPPZD</t>
+          <t>B0B42SWT68</t>
         </is>
       </c>
       <c r="D4" s="14"/>
@@ -6503,23 +6415,23 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>Tineco Corded Wet Dry Vacuum Steam Mop All-in-one, Hardwood Floor Cleaner Great for Sticky Messes, Floor ONE S5 Steam Smart f</t>
+          <t>Tineco iFLOOR 2 Complete Wet Dry Vacuum, Hard Floor, Cordlesssvacuums and washes simultaneously, dual-tank system, 90% wate</t>
         </is>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B09QFHPPZD?psc=1</t>
+          <t>https://www.amazon.com/dp/B0B42SWT68?psc=1</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61DuH1C9gWL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71yFNGDmpML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>B09QFHPPZD</t>
+          <t>B0B42SWT68</t>
         </is>
       </c>
       <c r="M4" s="1"/>
@@ -6536,17 +6448,17 @@
       <c r="X4" s="15"/>
       <c r="Y4"/>
       <c r="Z4" s="19">
-        <v>229</v>
+        <v>149</v>
       </c>
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
       <c r="AD4" s="20">
-        <v>1377</v>
+        <v>2385</v>
       </c>
       <c r="AE4"/>
       <c r="AF4" s="21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG4" s="22">
         <v>0</v>
@@ -6598,7 +6510,7 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B0B42SWT68</t>
+          <t>B0BKZTZM19</t>
         </is>
       </c>
       <c r="D5" s="14"/>
@@ -6611,23 +6523,23 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Tineco iFLOOR 2 Complete Wet Dry Vacuum, Hard Floor, Cordlesssvacuums and washes simultaneously, dual-tank system, 90% wate</t>
+          <t>DREAME H12 PRO Vacuum Mop, Wet Dry Vacuum Cleaner for Hard Floor, Vacuum and Mop at The Same Time for Wet &amp; Dry Messes, Auto</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0B42SWT68?psc=1</t>
+          <t>https://www.amazon.com/dp/B0BKZTZM19?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71yFNGDmpML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61X2SQZjobL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B0B42SWT68</t>
+          <t>B0BKZTZM19</t>
         </is>
       </c>
       <c r="M5" s="1"/>
@@ -6644,17 +6556,17 @@
       <c r="X5" s="15"/>
       <c r="Y5"/>
       <c r="Z5" s="19">
-        <v>149</v>
+        <v>219.99</v>
       </c>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5" s="20">
-        <v>2385</v>
+        <v>3391</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" s="21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG5" s="22">
         <v>0</v>
@@ -6706,7 +6618,7 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0BKZTZM19</t>
+          <t>B0C2P8SS2Y</t>
         </is>
       </c>
       <c r="D6" s="14"/>
@@ -6719,23 +6631,23 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>DREAME H12 PRO Vacuum Mop, Wet Dry Vacuum Cleaner for Hard Floor, Vacuum and Mop at The Same Time for Wet &amp; Dry Messes, Auto</t>
+          <t>DREAME H12 Dual Vacuum Mop, 4-in-1 Cordless Vacuum Mop Combo, Wet Dry Vacuum Cleaner for Hard Floor, Cordless Vacuum for Mult</t>
         </is>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BKZTZM19?psc=1</t>
+          <t>https://www.amazon.com/dp/B0C2P8SS2Y?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61X2SQZjobL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71gAfXzEZdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0BKZTZM19</t>
+          <t>B0C2P8SS2Y</t>
         </is>
       </c>
       <c r="M6" s="1"/>
@@ -6752,17 +6664,17 @@
       <c r="X6" s="15"/>
       <c r="Y6"/>
       <c r="Z6" s="19">
-        <v>219.99</v>
+        <v>267.79</v>
       </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6" s="20">
-        <v>3391</v>
+        <v>343</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" s="21">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AG6" s="22">
         <v>0</v>
@@ -6814,7 +6726,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B0C2P8SS2Y</t>
+          <t>B0C7L8897L</t>
         </is>
       </c>
       <c r="D7" s="14"/>
@@ -6827,23 +6739,23 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>DREAME H12 Dual Vacuum Mop, 4-in-1 Cordless Vacuum Mop Combo, Wet Dry Vacuum Cleaner for Hard Floor, Cordless Vacuum for Mult</t>
+          <t>Eureka Wet Dry Vacuum Cleaner Cordless, Mop Vacuum Cleaner with Self-Cleaning System, Lightweight Hardwood Floors Vacuum for</t>
         </is>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C2P8SS2Y?psc=1</t>
+          <t>https://www.amazon.com/dp/B0C7L8897L?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71gAfXzEZdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/614e+7HOyAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B0C2P8SS2Y</t>
+          <t>B0C7L8897L</t>
         </is>
       </c>
       <c r="M7" s="1"/>
@@ -6860,13 +6772,13 @@
       <c r="X7" s="15"/>
       <c r="Y7"/>
       <c r="Z7" s="19">
-        <v>267.79</v>
+        <v>159.99</v>
       </c>
       <c r="AA7"/>
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7" s="20">
-        <v>343</v>
+        <v>894</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" s="21">
@@ -6922,7 +6834,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B0C7L8897L</t>
+          <t>B0CB21PRJB</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -6935,23 +6847,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Eureka Wet Dry Vacuum Cleaner Cordless, Mop Vacuum Cleaner with Self-Cleaning System, Lightweight Hardwood Floors Vacuum for</t>
+          <t>Shark MessMaster Portable Wet/Dry Vac, 3 Tools + Extension Wand, VS101s1-Gallon Capacity, AnyBag Tech, Self-Clean, Powerful</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C7L8897L?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CB21PRJB?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/614e+7HOyAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81c+Fd4c0LL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B0C7L8897L</t>
+          <t>B0CB21PRJB</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -6968,17 +6880,17 @@
       <c r="X8" s="15"/>
       <c r="Y8"/>
       <c r="Z8" s="19">
-        <v>159.99</v>
+        <v>139</v>
       </c>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="20">
-        <v>894</v>
+        <v>1317</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="21">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AG8" s="22">
         <v>0</v>
@@ -7030,7 +6942,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B0CB21PRJB</t>
+          <t>B0CMV9PYRQ</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -7043,23 +6955,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Shark MessMaster Portable Wet/Dry Vac, 3 Tools + Extension Wand, VS101s1-Gallon Capacity, AnyBag Tech, Self-Clean, Powerful</t>
+          <t>Bissell CrossWave OmniForce Cordless Wet Dry Vacuum Mop, 3882sDedicated dry vacuum mode; tangle-free brush roll; multi-surf</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CB21PRJB?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CMV9PYRQ?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81c+Fd4c0LL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71SwH11djQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B0CB21PRJB</t>
+          <t>B0CMV9PYRQ</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -7076,17 +6988,17 @@
       <c r="X9" s="15"/>
       <c r="Y9"/>
       <c r="Z9" s="19">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="AA9"/>
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="20">
-        <v>1317</v>
+        <v>1497</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="21">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG9" s="22">
         <v>0</v>
@@ -7138,7 +7050,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0CMV9PYRQ</t>
+          <t>B0CRR8FJSD</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -7151,23 +7063,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Bissell CrossWave OmniForce Cordless Wet Dry Vacuum Mop, 3882sDedicated dry vacuum mode; tangle-free brush roll; multi-surf</t>
+          <t>Tineco iFLOOR 5 Breeze Complete Wet Dry Vacuum Cordless Floor Washer, One-Step Cleaning for Hard Floors, Edge Clean, Auto Sel</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CMV9PYRQ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CRR8FJSD?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71SwH11djQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0CMV9PYRQ</t>
+          <t>B0CRR8FJSD</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7184,17 +7096,17 @@
       <c r="X10" s="15"/>
       <c r="Y10"/>
       <c r="Z10" s="19">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AA10"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="20">
-        <v>1497</v>
+        <v>2736</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG10" s="22">
         <v>0</v>
@@ -7246,7 +7158,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0CRR8FJSD</t>
+          <t>B0CRVTSRKH</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -7259,23 +7171,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Tineco iFLOOR 5 Breeze Complete Wet Dry Vacuum Cordless Floor Washer, One-Step Cleaning for Hard Floors, Edge Clean, Auto Sel</t>
+          <t>Tineco Floor ONE S7 FlashDry Smart Cordless Wet Dry Vacuum Cleaner, Long Runtime, Great for Sticky Messes, Self-Cleaning, 158</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CRR8FJSD?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CRVTSRKH?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61mFlJzaWqL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0CRR8FJSD</t>
+          <t>B0CRVTSRKH</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7292,17 +7204,17 @@
       <c r="X11" s="15"/>
       <c r="Y11"/>
       <c r="Z11" s="19">
-        <v>189</v>
+        <v>349</v>
       </c>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="20">
-        <v>2736</v>
+        <v>1058</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG11" s="22">
         <v>0</v>
@@ -7354,7 +7266,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0CRVTSRKH</t>
+          <t>B0CVXLXGRP</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -7367,23 +7279,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor ONE S7 FlashDry Smart Cordless Wet Dry Vacuum Cleaner, Long Runtime, Great for Sticky Messes, Self-Cleaning, 158</t>
+          <t>Tineco Floor ONE Stretch S6 Cordless Wet Dry Vacuum Cleaner, 180°Lay-Flat Smart Vacuum Mop, 40 Minutes Long Runtime 158℉ Flas</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CRVTSRKH?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CVXLXGRP?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61mFlJzaWqL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0CRVTSRKH</t>
+          <t>B0CVXLXGRP</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7400,17 +7312,17 @@
       <c r="X12" s="15"/>
       <c r="Y12"/>
       <c r="Z12" s="19">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="20">
-        <v>1058</v>
+        <v>1128</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG12" s="22">
         <v>0</v>
@@ -7462,7 +7374,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0CVXLXGRP</t>
+          <t>B0CWV3C423</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -7475,23 +7387,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor ONE Stretch S6 Cordless Wet Dry Vacuum Cleaner, 180°Lay-Flat Smart Vacuum Mop, 40 Minutes Long Runtime 158℉ Flas</t>
+          <t>dreame H14 Cordless Vacuum Mop, 180° Lie-Flat Wet Dry Vacuum cleaner, 140°F Brush Washing, Fast Hot Air Drying in 5Mins, Smar</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CVXLXGRP?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CWV3C423?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61v-UPCYmVL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0CVXLXGRP</t>
+          <t>B0CWV3C423</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7508,17 +7420,17 @@
       <c r="X13" s="15"/>
       <c r="Y13"/>
       <c r="Z13" s="19">
-        <v>379</v>
+        <v>349.99</v>
       </c>
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="20">
-        <v>1128</v>
+        <v>720</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
@@ -7570,7 +7482,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0CWV3C423</t>
+          <t>B0D5234PWF</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7583,23 +7495,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>dreame H14 Cordless Vacuum Mop, 180° Lie-Flat Wet Dry Vacuum cleaner, 140°F Brush Washing, Fast Hot Air Drying in 5Mins, Smar</t>
+          <t>Bissell CrossWave OmniFind Cordless Wet Dry Vacuum Mop, 3967FsFurFinder headlights to spot pet hair; powerful all-in-one su</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CWV3C423?psc=1</t>
+          <t>https://www.amazon.com/dp/B0D5234PWF?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61v-UPCYmVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71C1hPHlipL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0CWV3C423</t>
+          <t>B0D5234PWF</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7616,17 +7528,17 @@
       <c r="X14" s="15"/>
       <c r="Y14"/>
       <c r="Z14" s="19">
-        <v>349.99</v>
+        <v>229.99</v>
       </c>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="20">
-        <v>720</v>
+        <v>438</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="21">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG14" s="22">
         <v>0</v>
@@ -7678,7 +7590,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0D5234PWF</t>
+          <t>B0D97D5XHH</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7691,23 +7603,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Bissell CrossWave OmniFind Cordless Wet Dry Vacuum Mop, 3967FsFurFinder headlights to spot pet hair; powerful all-in-one su</t>
+          <t>JONR ED12 Vacuum Cleaner Wet and Dry, Cordless Floor Cleaner Machine with Self-Cleaning, Dual Tank Design, 0.1 inch Edge Clea</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0D5234PWF?psc=1</t>
+          <t>https://www.amazon.com/dp/B0D97D5XHH?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71C1hPHlipL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61J-JX8alAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0D5234PWF</t>
+          <t>B0D97D5XHH</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7724,17 +7636,17 @@
       <c r="X15" s="15"/>
       <c r="Y15"/>
       <c r="Z15" s="19">
-        <v>229.99</v>
+        <v>144.92</v>
       </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="20">
-        <v>438</v>
+        <v>538</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="21">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
@@ -7786,7 +7698,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0D97D5XHH</t>
+          <t>B0D9Q1CQMF</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7799,23 +7711,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>JONR ED12 Vacuum Cleaner Wet and Dry, Cordless Floor Cleaner Machine with Self-Cleaning, Dual Tank Design, 0.1 inch Edge Clea</t>
+          <t>NARWAL S20 Pro Cordless Vacuum Mop with Self-Cleaning, Wet Dry Vacuum Cleaner for Hard Floors, Ideal for Families with Kids a</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0D97D5XHH?psc=1</t>
+          <t>https://www.amazon.com/dp/B0D9Q1CQMF?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61J-JX8alAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61EHeq1VmiL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0D97D5XHH</t>
+          <t>B0D9Q1CQMF</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7832,13 +7744,13 @@
       <c r="X16" s="15"/>
       <c r="Y16"/>
       <c r="Z16" s="19">
-        <v>144.92</v>
+        <v>359.99</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="20">
-        <v>538</v>
+        <v>845</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="21">
@@ -7894,7 +7806,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0D9Q1CQMF</t>
+          <t>B0DHTW17RR</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7907,23 +7819,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>NARWAL S20 Pro Cordless Vacuum Mop with Self-Cleaning, Wet Dry Vacuum Cleaner for Hard Floors, Ideal for Families with Kids a</t>
+          <t>roborock F25 XT Wet Dry Vacuum Mop, Cordless Vacuum Cleaner, APP ControlsSelf-Propelled Assist Wheels, Auto Detergent Dispe</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0D9Q1CQMF?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DHTW17RR?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61EHeq1VmiL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71HN6zSJ4VL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0D9Q1CQMF</t>
+          <t>B0DHTW17RR</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7946,11 +7858,11 @@
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="20">
-        <v>845</v>
+        <v>5068</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG17" s="22">
         <v>0</v>
@@ -8002,7 +7914,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0DHTW17RR</t>
+          <t>B0DNG786P1</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -8015,23 +7927,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>roborock F25 XT Wet Dry Vacuum Mop, Cordless Vacuum Cleaner, APP ControlsSelf-Propelled Assist Wheels, Auto Detergent Dispe</t>
+          <t>Bissell CrossWave HydroSteam Deluxe 3-in-1 Steam Mop, 3515GsDeluxe steam function for deep sanitizing; sanitize formula inc</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DHTW17RR?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DNG786P1?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71HN6zSJ4VL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71U3O0HN1ZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0DHTW17RR</t>
+          <t>B0DNG786P1</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8048,17 +7960,17 @@
       <c r="X18" s="15"/>
       <c r="Y18"/>
       <c r="Z18" s="19">
-        <v>359.99</v>
+        <v>279.99</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="20">
-        <v>5068</v>
+        <v>718</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
@@ -8110,7 +8022,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0DNG786P1</t>
+          <t>B0DPPLWYGX</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8123,23 +8035,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Bissell CrossWave HydroSteam Deluxe 3-in-1 Steam Mop, 3515GsDeluxe steam function for deep sanitizing; sanitize formula inc</t>
+          <t>Tineco Floor ONE S7 Stretch Ultra Cordless Wet Dry Vacuum Cleaner, 180°Lay-Flat Anti-Tangle Design, 50 Minutes Runtime, 185℉</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DNG786P1?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DPPLWYGX?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71U3O0HN1ZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61zNj-9L5UL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0DNG786P1</t>
+          <t>B0DPPLWYGX</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8156,17 +8068,17 @@
       <c r="X19" s="15"/>
       <c r="Y19"/>
       <c r="Z19" s="19">
-        <v>279.99</v>
+        <v>449</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="20">
-        <v>718</v>
+        <v>2870</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -8218,7 +8130,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0DPPLWYGX</t>
+          <t>B0DQ7HD168</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8231,23 +8143,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor ONE S7 Stretch Ultra Cordless Wet Dry Vacuum Cleaner, 180°Lay-Flat Anti-Tangle Design, 50 Minutes Runtime, 185℉</t>
+          <t>roborock F25 GT Gen 2 Wet Dry Vacuum Cleaner, Cordless Vacuum Mop Combos20000Pa Suction, 194°F Self-Cleaning Electric Mop,</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DPPLWYGX?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DQ7HD168?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61zNj-9L5UL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51e70-aZRJL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0DPPLWYGX</t>
+          <t>B0DQ7HD168</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8264,17 +8176,17 @@
       <c r="X20" s="15"/>
       <c r="Y20"/>
       <c r="Z20" s="19">
-        <v>449</v>
+        <v>299.99</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="20">
-        <v>2870</v>
+        <v>2195</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -8326,7 +8238,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0DQ7HD168</t>
+          <t>B0DS2389H1</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8339,23 +8251,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>roborock F25 GT Gen 2 Wet Dry Vacuum Cleaner, Cordless Vacuum Mop Combos20000Pa Suction, 194°F Self-Cleaning Electric Mop,</t>
+          <t>dreame G10 Pro Wet Dry Vacuum Mop, Vacuum and Mop All in One for Hard FloorsAuto Self-Cleaning, 16K Pa Powerful Suction, Up</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DQ7HD168?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DS2389H1?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51e70-aZRJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71RGba78P7L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0DQ7HD168</t>
+          <t>B0DS2389H1</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8372,17 +8284,17 @@
       <c r="X21" s="15"/>
       <c r="Y21"/>
       <c r="Z21" s="19">
-        <v>299.99</v>
+        <v>159.99</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="20">
-        <v>2195</v>
+        <v>607</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
@@ -8434,7 +8346,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0DS2389H1</t>
+          <t>B0DY7G7C8P</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8447,23 +8359,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>dreame G10 Pro Wet Dry Vacuum Mop, Vacuum and Mop All in One for Hard FloorsAuto Self-Cleaning, 16K Pa Powerful Suction, Up</t>
+          <t>Tineco Floor One S9 Artist Steam Wet Dry Vacuum Cleaner, High-Temp Steam Cleaning, 22kPa Suction, 360° SmoothDrive, Anti-Tang</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DS2389H1?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DY7G7C8P?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71RGba78P7L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61DHdYz-K5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0DS2389H1</t>
+          <t>B0DY7G7C8P</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8480,17 +8392,17 @@
       <c r="X22" s="15"/>
       <c r="Y22"/>
       <c r="Z22" s="19">
-        <v>159.99</v>
+        <v>749</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="20">
-        <v>607</v>
+        <v>232</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -8542,7 +8454,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0DY7G7C8P</t>
+          <t>B0F138D56C</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8555,23 +8467,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor One S9 Artist Steam Wet Dry Vacuum Cleaner, High-Temp Steam Cleaning, 22kPa Suction, 360° SmoothDrive, Anti-Tang</t>
+          <t>dreame H15 Pro Heat Wet Dry Vacuum and Mop, 185°F Hot Water Floor Cleanings0 Hair Tangle for Pet, Vacuum Cleaner with AI Ro</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DY7G7C8P?psc=1</t>
+          <t>https://www.amazon.com/dp/B0F138D56C?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61DHdYz-K5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61Tj-nSo4pL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0DY7G7C8P</t>
+          <t>B0F138D56C</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8588,17 +8500,17 @@
       <c r="X23" s="15"/>
       <c r="Y23"/>
       <c r="Z23" s="19">
-        <v>749</v>
+        <v>649.99</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="20">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -8650,7 +8562,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0F138D56C</t>
+          <t>B0F3GYMWG5</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8663,23 +8575,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>dreame H15 Pro Heat Wet Dry Vacuum and Mop, 185°F Hot Water Floor Cleanings0 Hair Tangle for Pet, Vacuum Cleaner with AI Ro</t>
+          <t>Tineco Floor ONE i5 Stretch Wet Dry Vacuum Cleaner, Vacuum &amp; Mop in One Step, 20kpa Powerful Suction, 180° Lay-Flat Design, A</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0F138D56C?psc=1</t>
+          <t>https://www.amazon.com/dp/B0F3GYMWG5?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61Tj-nSo4pL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0F138D56C</t>
+          <t>B0F3GYMWG5</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8696,17 +8608,17 @@
       <c r="X24" s="15"/>
       <c r="Y24"/>
       <c r="Z24" s="19">
-        <v>649.99</v>
+        <v>239</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="20">
-        <v>146</v>
+        <v>970</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -8758,7 +8670,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0F3GYMWG5</t>
+          <t>B0FHHRXJ56</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8771,23 +8683,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor ONE i5 Stretch Wet Dry Vacuum Cleaner, Vacuum &amp; Mop in One Step, 20kpa Powerful Suction, 180° Lay-Flat Design, A</t>
+          <t>roborock F25 Ultra Steam Wet Dry Vacuum Mop, 356°F Steam, 187°F Hot WatersCordless Vacuum Mop and Cleaner, Floor Steamer wi</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0F3GYMWG5?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FHHRXJ56?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71f-121xiOL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0F3GYMWG5</t>
+          <t>B0FHHRXJ56</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8804,17 +8716,17 @@
       <c r="X25" s="15"/>
       <c r="Y25"/>
       <c r="Z25" s="19">
-        <v>239</v>
+        <v>479.99</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="20">
-        <v>970</v>
+        <v>2613</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -8866,7 +8778,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FHHRXJ56</t>
+          <t>B0FL781KTH</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8879,23 +8791,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>roborock F25 Ultra Steam Wet Dry Vacuum Mop, 356°F Steam, 187°F Hot WatersCordless Vacuum Mop and Cleaner, Floor Steamer wi</t>
+          <t>Tineco Floor One Switch S6 Stretch Breeze Wet Dry Vacuum Cleaners, Floor Cleaner Mop 2-in-1 Cordless Vacuum for Multi-Surface</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FHHRXJ56?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FL781KTH?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71f-121xiOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71lwDHodFbL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FHHRXJ56</t>
+          <t>B0FL781KTH</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8912,17 +8824,17 @@
       <c r="X26" s="15"/>
       <c r="Y26"/>
       <c r="Z26" s="19">
-        <v>479.99</v>
+        <v>449</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="20">
-        <v>2613</v>
+        <v>73</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="21">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -8974,7 +8886,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FL781KTH</t>
+          <t>B0FLJPZD5B</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8987,23 +8899,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor One Switch S6 Stretch Breeze Wet Dry Vacuum Cleaners, Floor Cleaner Mop 2-in-1 Cordless Vacuum for Multi-Surface</t>
+          <t>DREAME H15 Pro CarpetFlex Cordless Vacuum Mop, Wet Dry Vacuum Cleaner with Dual Brushes for Hard Floors &amp; Carpet, Tangle-Free</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FL781KTH?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FLJPZD5B?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71lwDHodFbL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71YWxGjWSZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FL781KTH</t>
+          <t>B0FLJPZD5B</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -9019,18 +8931,16 @@
       <c r="W27" s="15"/>
       <c r="X27" s="15"/>
       <c r="Y27"/>
-      <c r="Z27" s="19">
-        <v>449</v>
-      </c>
+      <c r="Z27" s="19"/>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="20">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -9082,7 +8992,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FLJPZD5B</t>
+          <t>B0FLQ68XSW</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9095,23 +9005,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>DREAME H15 Pro CarpetFlex Cordless Vacuum Mop, Wet Dry Vacuum Cleaner with Dual Brushes for Hard Floors &amp; Carpet, Tangle-Free</t>
+          <t>Tineco Corded 3-in-1 Wet Dry Vacuum Mop with Steam Function, FLOOR ONE S6 Stretch Steam, Tineco BoostSteam, 320℉ High-temp St</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FLJPZD5B?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FLQ68XSW?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71YWxGjWSZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61YxVL4HTtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FLJPZD5B</t>
+          <t>B0FLQ68XSW</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9127,16 +9037,18 @@
       <c r="W28" s="15"/>
       <c r="X28" s="15"/>
       <c r="Y28"/>
-      <c r="Z28" s="19"/>
+      <c r="Z28" s="19">
+        <v>399</v>
+      </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="20">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -9188,7 +9100,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FLQ68XSW</t>
+          <t>B0FX9CDKGB</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9201,23 +9113,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Tineco Corded 3-in-1 Wet Dry Vacuum Mop with Steam Function, FLOOR ONE S6 Stretch Steam, Tineco BoostSteam, 320℉ High-temp St</t>
+          <t>Tineco Floor ONE S6 Master Wet Dry Vacuum Cleaner, 20kPa Suction Vacuum Mop with Dual-Edge Cleaning, 45 Min Runtime (Quite Mo</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FLQ68XSW?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FX9CDKGB?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61YxVL4HTtL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71wpqOUZVdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FLQ68XSW</t>
+          <t>B0FX9CDKGB</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9234,17 +9146,17 @@
       <c r="X29" s="15"/>
       <c r="Y29"/>
       <c r="Z29" s="19">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="20">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="21">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -9296,7 +9208,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FX9CDKGB</t>
+          <t>B0G2MXVLP1</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9309,23 +9221,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor ONE S6 Master Wet Dry Vacuum Cleaner, 20kPa Suction Vacuum Mop with Dual-Edge Cleaning, 45 Min Runtime (Quite Mo</t>
+          <t>BISSELL CrossWave Edge Cordless Wet Dry Vacuum with Edge Cleaning, Tangle-Free Pet Hair Brush Roll, FreshStart Filter, and St</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FX9CDKGB?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G2MXVLP1?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71wpqOUZVdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71UEOWV8bNL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FX9CDKGB</t>
+          <t>B0G2MXVLP1</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9342,17 +9254,17 @@
       <c r="X30" s="15"/>
       <c r="Y30"/>
       <c r="Z30" s="19">
-        <v>349</v>
+        <v>249.99</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="20">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="21">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -9404,7 +9316,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0G2MXVLP1</t>
+          <t>B0G2P53KJR</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9417,23 +9329,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>BISSELL CrossWave Edge Cordless Wet Dry Vacuum with Edge Cleaning, Tangle-Free Pet Hair Brush Roll, FreshStart Filter, and St</t>
+          <t>Bissell CrossWave Edge Cordless Plus Wet Dry Vacuum &amp; Mop, 4329GsExtra brush rolls, filters &amp; hard floor cleaner included;</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G2MXVLP1?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G2P53KJR?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71UEOWV8bNL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81J1mKjTT8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0G2MXVLP1</t>
+          <t>B0G2P53KJR</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9450,17 +9362,17 @@
       <c r="X31" s="15"/>
       <c r="Y31"/>
       <c r="Z31" s="19">
-        <v>249.99</v>
+        <v>219.99</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="20">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -9512,7 +9424,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0G2P53KJR</t>
+          <t>B0G3RT4R7C</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9525,23 +9437,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Bissell CrossWave Edge Cordless Plus Wet Dry Vacuum &amp; Mop, 4329GsExtra brush rolls, filters &amp; hard floor cleaner included;</t>
+          <t>BISSELL CrossWave HydroScrub Plus Cordless Wet Dry Vacuum Mop, Floor Cleaner with Edge Cleaning &amp; Headlights, 45-Minute Runti</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G2P53KJR?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G3RT4R7C?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81J1mKjTT8L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81Kv8NtfkFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0G2P53KJR</t>
+          <t>B0G3RT4R7C</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9558,17 +9470,17 @@
       <c r="X32" s="15"/>
       <c r="Y32"/>
       <c r="Z32" s="19">
-        <v>219.99</v>
+        <v>319.99</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="20">
-        <v>257</v>
+        <v>85</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="21">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
@@ -9620,7 +9532,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0G3RT4R7C</t>
+          <t>B0G4W2GMRS</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9633,23 +9545,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>BISSELL CrossWave HydroScrub Plus Cordless Wet Dry Vacuum Mop, Floor Cleaner with Edge Cleaning &amp; Headlights, 45-Minute Runti</t>
+          <t>DREAME Aero Pro Wet Dry Vacuum Mop, Ultra-Slim with Hot Self-Cleaning/Self-Drying, 0 Hair Tangle Great for Pet Owner, Powerfu</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G3RT4R7C?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G4W2GMRS?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81Kv8NtfkFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61sDpXvYzHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0G3RT4R7C</t>
+          <t>B0G4W2GMRS</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9666,17 +9578,17 @@
       <c r="X33" s="15"/>
       <c r="Y33"/>
       <c r="Z33" s="19">
-        <v>319.99</v>
+        <v>379.96</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="20">
-        <v>85</v>
+        <v>294</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="21">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
@@ -9728,7 +9640,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0G4W2GMRS</t>
+          <t>B0GDZBQV83</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9741,23 +9653,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>DREAME Aero Pro Wet Dry Vacuum Mop, Ultra-Slim with Hot Self-Cleaning/Self-Drying, 0 Hair Tangle Great for Pet Owner, Powerfu</t>
+          <t>NARWAL S30 Wet Dry Vacuum Cleaner with 20000Pa Suction, 176°F Self-Cleaning, Heated Drying, Disposable Waste Bag, Tangle-Free</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G4W2GMRS?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GDZBQV83?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61sDpXvYzHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51MR6wHXuGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0G4W2GMRS</t>
+          <t>B0GDZBQV83</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9774,17 +9686,17 @@
       <c r="X34" s="15"/>
       <c r="Y34"/>
       <c r="Z34" s="19">
-        <v>379.96</v>
+        <v>152.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="20">
-        <v>294</v>
+        <v>3</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -9836,7 +9748,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GDZBQV83</t>
+          <t>B0GH3FSR4D</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9849,23 +9761,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>NARWAL S30 Wet Dry Vacuum Cleaner with 20000Pa Suction, 176°F Self-Cleaning, Heated Drying, Disposable Waste Bag, Tangle-Free</t>
+          <t>Dyson Clean+Wash Hygiene Wet and Dry Cleaner for Hard Floors - Cordless, 70 Minutes Run time, lays Flat, Anti-Tangle, self-Cl</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GDZBQV83?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GH3FSR4D?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51MR6wHXuGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61U0uZOviIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GDZBQV83</t>
+          <t>B0GH3FSR4D</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9882,17 +9794,17 @@
       <c r="X35" s="15"/>
       <c r="Y35"/>
       <c r="Z35" s="19">
-        <v>152.99</v>
+        <v>499.99</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="20">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="21">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
@@ -9944,7 +9856,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GH3FSR4D</t>
+          <t>B0GSKPS7BZ</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9957,23 +9869,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Dyson Clean+Wash Hygiene Wet and Dry Cleaner for Hard Floors - Cordless, 70 Minutes Run time, lays Flat, Anti-Tangle, self-Cl</t>
+          <t>Redroad Wet Dry Vacuum Cleaner 20,000Pa,50Mins Runtime Cleaning Area 3013ft²,Cordless Vacuum Cleaner, Cordless Vacuum and Mop</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GH3FSR4D?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GSKPS7BZ?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61U0uZOviIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61MFjSLQThL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GH3FSR4D</t>
+          <t>B0GSKPS7BZ</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9990,17 +9902,17 @@
       <c r="X36" s="15"/>
       <c r="Y36"/>
       <c r="Z36" s="19">
-        <v>499.99</v>
+        <v>159.99</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="20">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="21">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG36" s="22">
         <v>0</v>
@@ -10052,7 +9964,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GSKPS7BZ</t>
+          <t>B0GSWSYTVH</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10065,23 +9977,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Redroad Wet Dry Vacuum Cleaner 20,000Pa,50Mins Runtime Cleaning Area 3013ft²,Cordless Vacuum Cleaner, Cordless Vacuum and Mop</t>
+          <t>Bissell CrossWave Reach Plus Wet Dry Vacuum and Mop, 4506FsVacuums, mops, and sanitizes together, self-dries in a hot air d</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GSKPS7BZ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GSWSYTVH?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61MFjSLQThL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Vj2UTHenL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GSKPS7BZ</t>
+          <t>B0GSWSYTVH</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10098,17 +10010,17 @@
       <c r="X37" s="15"/>
       <c r="Y37"/>
       <c r="Z37" s="19">
-        <v>159.99</v>
+        <v>249.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="20">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="21">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
@@ -10160,7 +10072,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GSWSYTVH</t>
+          <t>B0GVJ8VWRG</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10173,23 +10085,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Bissell CrossWave Reach Plus Wet Dry Vacuum and Mop, 4506FsVacuums, mops, and sanitizes together, self-dries in a hot air d</t>
+          <t>Tineco Floor ONE Station S9 Scientist Pro Vacuum Mop with 5L Water StoragesThe Latest Generation Wet Dry Vacuum Cleaner wit</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GSWSYTVH?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GVJ8VWRG?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Vj2UTHenL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61zyPjyvN0L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GSWSYTVH</t>
+          <t>B0GVJ8VWRG</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10206,17 +10118,17 @@
       <c r="X38" s="15"/>
       <c r="Y38"/>
       <c r="Z38" s="19">
-        <v>249.99</v>
+        <v>1199</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG38" s="22">
         <v>0</v>
@@ -10268,7 +10180,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GVJ8VWRG</t>
+          <t>B0GWPHZ5XW</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10281,23 +10193,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor ONE Station S9 Scientist Pro Vacuum Mop with 5L Water StoragesThe Latest Generation Wet Dry Vacuum Cleaner wit</t>
+          <t>DREAME Aero Pro Steam Wet Dry Vacuum Mop, 392℉ Steam Cleaning, 28kPa Suction, 3.88in Ultra-Slim Vacuum Mop Combo, 0 Hair Tang</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GVJ8VWRG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GWPHZ5XW?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61zyPjyvN0L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61CFmCWgPvL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GVJ8VWRG</t>
+          <t>B0GWPHZ5XW</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10314,17 +10226,17 @@
       <c r="X39" s="15"/>
       <c r="Y39"/>
       <c r="Z39" s="19">
-        <v>1199</v>
+        <v>599.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="20">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="21">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
@@ -10376,7 +10288,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GWPHZ5XW</t>
+          <t>B0GXDZGMR6</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10389,23 +10301,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>DREAME Aero Pro Steam Wet Dry Vacuum Mop, 392℉ Steam Cleaning, 28kPa Suction, 3.88in Ultra-Slim Vacuum Mop Combo, 0 Hair Tang</t>
+          <t>dreame FloorX 110 Plus Wet Dry Mop, Cordless Wet Dry Cleaner, Eletric MopsPicks Up Debris, 600RPM Scrubbing, 149°F Hot Air</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GWPHZ5XW?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GXDZGMR6?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61CFmCWgPvL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51CBvrPg5DL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GWPHZ5XW</t>
+          <t>B0GXDZGMR6</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10422,17 +10334,17 @@
       <c r="X40" s="15"/>
       <c r="Y40"/>
       <c r="Z40" s="19">
-        <v>599.99</v>
+        <v>123.49</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="20">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="21">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AG40" s="22">
         <v>0</v>
@@ -10484,7 +10396,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GXDZGMR6</t>
+          <t>B0H1X526LW</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10497,23 +10409,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>dreame FloorX 110 Plus Wet Dry Mop, Cordless Wet Dry Cleaner, Eletric MopsPicks Up Debris, 600RPM Scrubbing, 149°F Hot Air</t>
+          <t>DREAME Aero Ultra Steam Vacuum Mop, 392℉ Steam, 194℉ Hot Water, FoamWashsWet Dry Vacuum with 30kPa Suction, 3.88in Slim Flo</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GXDZGMR6?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H1X526LW?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51CBvrPg5DL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61Yuy5vtWFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GXDZGMR6</t>
+          <t>B0H1X526LW</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10530,17 +10442,17 @@
       <c r="X41" s="15"/>
       <c r="Y41"/>
       <c r="Z41" s="19">
-        <v>123.49</v>
+        <v>799.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="20">
-        <v>267</v>
+        <v>45</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="21">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG41" s="22">
         <v>0</v>
@@ -10592,7 +10504,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0GY5Z5BT4</t>
+          <t>B0H41F4Q7Q</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10605,23 +10517,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Dyson V16 Piston Animal Submarine™ Cordless Wet and Dry Vacuums315AW, 70 min runtime, 3 Advanced cleaner heads for Carpet,</t>
+          <t>OLIXIS Wet Dry Vacuum Cleaner, Cordless All-in-One Vac Mops, Vacuum Mop with Self-Cleaning System, Dual Water Tank Design, Ta</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GY5Z5BT4?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H41F4Q7Q?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61QCWF0RVJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61uSOtfOTBL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0GY5Z5BT4</t>
+          <t>B0H41F4Q7Q</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10638,17 +10550,17 @@
       <c r="X42" s="15"/>
       <c r="Y42"/>
       <c r="Z42" s="19">
-        <v>949.99</v>
+        <v>98.91</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="20">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG42" s="22">
         <v>0</v>
@@ -10700,7 +10612,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H1X526LW</t>
+          <t>B0H4ZTQ666</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10713,23 +10625,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>DREAME Aero Ultra Steam Vacuum Mop, 392℉ Steam, 194℉ Hot Water, FoamWashsWet Dry Vacuum with 30kPa Suction, 3.88in Slim Flo</t>
+          <t>roborock F25 Pro Turbo Wet Dry Vacuum Mop, One-Tap Scrubbing Floor Cleaners25000Pa Cordless Wet Dry Vacuum Cleaner, Power-E</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H1X526LW?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H4ZTQ666?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61Yuy5vtWFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/6115RCOB5eL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H1X526LW</t>
+          <t>B0H4ZTQ666</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10746,17 +10658,17 @@
       <c r="X43" s="15"/>
       <c r="Y43"/>
       <c r="Z43" s="19">
-        <v>799.99</v>
+        <v>489.99</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="20">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="21">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG43" s="22">
         <v>0</v>
@@ -10808,7 +10720,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0H41F4Q7Q</t>
+          <t>B0H6QR43T8</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10821,23 +10733,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>OLIXIS Wet Dry Vacuum Cleaner, Cordless All-in-One Vac Mops, Vacuum Mop with Self-Cleaning System, Dual Water Tank Design, Ta</t>
+          <t>Roomba Electro 5in1 Disinfecting Hard Floor Cleaner, Kills 99.99% Germs &amp; Bacteria, Vacuum, Mop &amp; Sanitize in One Pass, Cordl</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H41F4Q7Q?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H6QR43T8?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61uSOtfOTBL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71sCLNoj7CL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0H41F4Q7Q</t>
+          <t>B0H6QR43T8</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10854,17 +10766,17 @@
       <c r="X44" s="15"/>
       <c r="Y44"/>
       <c r="Z44" s="19">
-        <v>98.91</v>
+        <v>329.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="20">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="21">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AG44" s="22">
         <v>0</v>
@@ -10916,7 +10828,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H4ZTQ666</t>
+          <t>B0H7CKW7T8</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10929,23 +10841,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>roborock F25 Pro Turbo Wet Dry Vacuum Mop, One-Tap Scrubbing Floor Cleaners25000Pa Cordless Wet Dry Vacuum Cleaner, Power-E</t>
+          <t>BROBIG Wet Dry Vacuum Mop - Self-Cleaning Floor Washer with 180°Lie-Flat &amp; 0 Hair Tangle, Self-Propelled Edge Cleaning, 60Min</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H4ZTQ666?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H7CKW7T8?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/6115RCOB5eL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61MqWVD4gLL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H4ZTQ666</t>
+          <t>B0H7CKW7T8</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10962,17 +10874,17 @@
       <c r="X45" s="15"/>
       <c r="Y45"/>
       <c r="Z45" s="19">
-        <v>489.99</v>
+        <v>199.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="20">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="21">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AG45" s="22">
         <v>0</v>
@@ -11024,7 +10936,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0H6QR43T8</t>
+          <t>B0H8SR916V</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -11037,23 +10949,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Roomba Electro 5in1 Disinfecting Hard Floor Cleaner, Kills 99.99% Germs &amp; Bacteria, Vacuum, Mop &amp; Sanitize in One Pass, Cordl</t>
+          <t>NEWBULIG Cordless Wet Dry Vacuum Mop Combo, Self-Cleaning, Anti-TanglesOne NEWBULIG wet dry vacuum mop for all floors. Self</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H6QR43T8?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H8SR916V?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71sCLNoj7CL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61gMXLDqhAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0H6QR43T8</t>
+          <t>B0H8SR916V</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11070,17 +10982,17 @@
       <c r="X46" s="15"/>
       <c r="Y46"/>
       <c r="Z46" s="19">
-        <v>329.99</v>
+        <v>95.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="20">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="21">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AG46" s="22">
         <v>0</v>
@@ -11132,7 +11044,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H7CKW7T8</t>
+          <t>B0HBRKPFZ1</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11145,23 +11057,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>BROBIG Wet Dry Vacuum Mop - Self-Cleaning Floor Washer with 180°Lie-Flat &amp; 0 Hair Tangle, Self-Propelled Edge Cleaning, 60Min</t>
+          <t>Shark AquaReach PRO Cordless Vacuum + Mop with Reach Wand, Charcoal, WD563sFor Hard Floors and Surfaces, One-Pass Wet &amp; Dry</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H7CKW7T8?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HBRKPFZ1?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61MqWVD4gLL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71OW-MoVElL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H7CKW7T8</t>
+          <t>B0HBRKPFZ1</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11178,17 +11090,17 @@
       <c r="X47" s="15"/>
       <c r="Y47"/>
       <c r="Z47" s="19">
-        <v>199.99</v>
+        <v>529.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="20">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
@@ -11240,7 +11152,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H8SR916V</t>
+          <t>B0HG12B1CH</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11253,23 +11165,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>NEWBULIG Cordless Wet Dry Vacuum Mop Combo, Self-Cleaning, Anti-TanglesOne NEWBULIG wet dry vacuum mop for all floors. Self</t>
+          <t>Ultenic Cordless Vacuum Mop Combo, Wet Dry Vacuum Cleaner, PurplesHandle Wet&amp;Dry Messes, 180° Lay-Flat &amp; Auto Self-Cleaning</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H8SR916V?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HG12B1CH?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61gMXLDqhAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Plsfn8YwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H8SR916V</t>
+          <t>B0HG12B1CH</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11286,17 +11198,17 @@
       <c r="X48" s="15"/>
       <c r="Y48"/>
       <c r="Z48" s="19">
-        <v>95.99</v>
+        <v>259.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="20">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="21">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
@@ -11348,7 +11260,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0HBRKPFZ1</t>
+          <t>B0HGM3QMZS</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11361,23 +11273,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Shark AquaReach PRO Cordless Vacuum + Mop with Reach Wand, Charcoal, WD563sFor Hard Floors and Surfaces, One-Pass Wet &amp; Dry</t>
+          <t>uwant Wet Dry Vacuum Cleaner, 180° Lay-Flat Vacuum Mop with 100℃ Hot Water Washing, Hot Air Drying, 23,000Pa Powerful Suction</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HBRKPFZ1?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HGM3QMZS?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71OW-MoVElL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61Sx+vwuVwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0HBRKPFZ1</t>
+          <t>B0HGM3QMZS</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11394,17 +11306,17 @@
       <c r="X49" s="15"/>
       <c r="Y49"/>
       <c r="Z49" s="19">
-        <v>529.99</v>
+        <v>399.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="20">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="21">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
@@ -11449,478 +11361,252 @@
       <c r="BQ49" s="23"/>
       <c r="BR49"/>
     </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0HG12B1CH</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.comundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>Ultenic Cordless Vacuum Mop Combo, Wet Dry Vacuum Cleaner, PurplesHandle Wet&amp;Dry Messes, 180° Lay-Flat &amp; Auto Self-Cleaning</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0HG12B1CH?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Plsfn8YwL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0HG12B1CH</t>
-        </is>
-      </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50"/>
-      <c r="Z50" s="19">
-        <v>259.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50" s="20">
-        <v>102</v>
-      </c>
-      <c r="AE50"/>
-      <c r="AF50" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="20"/>
-      <c r="AM50"/>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="20"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
-      <c r="BK50" s="23"/>
-      <c r="BL50"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HGM3QMZS</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.comundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>uwant Wet Dry Vacuum Cleaner, 180° Lay-Flat Vacuum Mop with 100℃ Hot Water Washing, Hot Air Drying, 23,000Pa Powerful Suction</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0HGM3QMZS?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61Sx+vwuVwL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HGM3QMZS</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="19">
-        <v>399.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="20">
-        <v>3</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="20"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="20"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.com/dp/B003R3JFJO"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.com/dp/B079WCPPQD"/>
     <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.com/dp/B003R3JFJO?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/71COfcQjt0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.com/dp/B003R3JFJO"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.com/dp/B079WCPPQD"/>
+    <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.com/dp/B079WCPPQD?psc=1"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-na.ssl-images-amazon.com/images/I/71THlFoTXFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.com/dp/B079WCPPQD"/>
+    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.com/dp/B09QFHPPZD"/>
     <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.com/dp/B079WCPPQD?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-na.ssl-images-amazon.com/images/I/71THlFoTXFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.com/dp/B079WCPPQD"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.com/dp/B09QFHPPZD"/>
+    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.com/dp/B09QFHPPZD?psc=1"/>
+    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-na.ssl-images-amazon.com/images/I/61DuH1C9gWL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.com/dp/B09QFHPPZD"/>
+    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.com/dp/B0B42SWT68"/>
     <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.com/dp/B09QFHPPZD?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-na.ssl-images-amazon.com/images/I/61DuH1C9gWL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.com/dp/B09QFHPPZD"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.com/dp/B0B42SWT68"/>
+    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.com/dp/B0B42SWT68?psc=1"/>
+    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-na.ssl-images-amazon.com/images/I/71yFNGDmpML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.com/dp/B0B42SWT68"/>
+    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.com/dp/B0BKZTZM19"/>
     <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.com/dp/B0B42SWT68?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-na.ssl-images-amazon.com/images/I/71yFNGDmpML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.com/dp/B0B42SWT68"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.com/dp/B0BKZTZM19"/>
+    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.com/dp/B0BKZTZM19?psc=1"/>
+    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-na.ssl-images-amazon.com/images/I/61X2SQZjobL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.com/dp/B0BKZTZM19"/>
+    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.com/dp/B0C2P8SS2Y"/>
     <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.com/dp/B0BKZTZM19?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-na.ssl-images-amazon.com/images/I/61X2SQZjobL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.com/dp/B0BKZTZM19"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.com/dp/B0C2P8SS2Y"/>
+    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.com/dp/B0C2P8SS2Y?psc=1"/>
+    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gAfXzEZdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.com/dp/B0C2P8SS2Y"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.com/dp/B0C7L8897L"/>
     <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.com/dp/B0C2P8SS2Y?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gAfXzEZdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.com/dp/B0C2P8SS2Y"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.com/dp/B0C7L8897L"/>
+    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.com/dp/B0C7L8897L?psc=1"/>
+    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-na.ssl-images-amazon.com/images/I/614e+7HOyAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.com/dp/B0C7L8897L"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.com/dp/B0CB21PRJB"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.com/dp/B0C7L8897L?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-na.ssl-images-amazon.com/images/I/614e+7HOyAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.com/dp/B0C7L8897L"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.com/dp/B0CB21PRJB"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.com/dp/B0CB21PRJB?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-na.ssl-images-amazon.com/images/I/81c+Fd4c0LL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.com/dp/B0CB21PRJB"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.com/dp/B0CMV9PYRQ"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.com/dp/B0CB21PRJB?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/81c+Fd4c0LL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.com/dp/B0CB21PRJB"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.com/dp/B0CMV9PYRQ"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.com/dp/B0CMV9PYRQ?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/71SwH11djQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.com/dp/B0CMV9PYRQ"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.com/dp/B0CRR8FJSD"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.com/dp/B0CMV9PYRQ?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-na.ssl-images-amazon.com/images/I/71SwH11djQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.com/dp/B0CMV9PYRQ"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.com/dp/B0CRR8FJSD"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.com/dp/B0CRR8FJSD?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-na.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.com/dp/B0CRR8FJSD"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.com/dp/B0CRVTSRKH"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.com/dp/B0CRR8FJSD?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-na.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.com/dp/B0CRR8FJSD"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.com/dp/B0CRVTSRKH"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.com/dp/B0CRVTSRKH?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-na.ssl-images-amazon.com/images/I/61mFlJzaWqL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.com/dp/B0CRVTSRKH"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.com/dp/B0CVXLXGRP"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.com/dp/B0CRVTSRKH?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-na.ssl-images-amazon.com/images/I/61mFlJzaWqL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.com/dp/B0CRVTSRKH"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.com/dp/B0CVXLXGRP"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.com/dp/B0CVXLXGRP?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-na.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.com/dp/B0CVXLXGRP"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.com/dp/B0CWV3C423"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.com/dp/B0CVXLXGRP?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-na.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.com/dp/B0CVXLXGRP"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.com/dp/B0CWV3C423"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.com/dp/B0CWV3C423?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-na.ssl-images-amazon.com/images/I/61v-UPCYmVL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.com/dp/B0CWV3C423"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.com/dp/B0D5234PWF"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.com/dp/B0CWV3C423?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-na.ssl-images-amazon.com/images/I/61v-UPCYmVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.com/dp/B0CWV3C423"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.com/dp/B0D5234PWF"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.com/dp/B0D5234PWF?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-na.ssl-images-amazon.com/images/I/71C1hPHlipL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.com/dp/B0D5234PWF"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.com/dp/B0D97D5XHH"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.com/dp/B0D5234PWF?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-na.ssl-images-amazon.com/images/I/71C1hPHlipL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.com/dp/B0D5234PWF"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.com/dp/B0D97D5XHH"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.com/dp/B0D97D5XHH?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-na.ssl-images-amazon.com/images/I/61J-JX8alAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.com/dp/B0D97D5XHH"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.com/dp/B0D9Q1CQMF"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.com/dp/B0D97D5XHH?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-na.ssl-images-amazon.com/images/I/61J-JX8alAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.com/dp/B0D97D5XHH"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.com/dp/B0D9Q1CQMF"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.com/dp/B0D9Q1CQMF?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-na.ssl-images-amazon.com/images/I/61EHeq1VmiL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.com/dp/B0D9Q1CQMF"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.com/dp/B0DHTW17RR"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.com/dp/B0D9Q1CQMF?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-na.ssl-images-amazon.com/images/I/61EHeq1VmiL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.com/dp/B0D9Q1CQMF"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.com/dp/B0DHTW17RR"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.com/dp/B0DHTW17RR?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-na.ssl-images-amazon.com/images/I/71HN6zSJ4VL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.com/dp/B0DHTW17RR"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.com/dp/B0DNG786P1"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.com/dp/B0DHTW17RR?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-na.ssl-images-amazon.com/images/I/71HN6zSJ4VL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.com/dp/B0DHTW17RR"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.com/dp/B0DNG786P1"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.com/dp/B0DNG786P1?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-na.ssl-images-amazon.com/images/I/71U3O0HN1ZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.com/dp/B0DNG786P1"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.com/dp/B0DPPLWYGX"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.com/dp/B0DNG786P1?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-na.ssl-images-amazon.com/images/I/71U3O0HN1ZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.com/dp/B0DNG786P1"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.com/dp/B0DPPLWYGX"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.com/dp/B0DPPLWYGX?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-na.ssl-images-amazon.com/images/I/61zNj-9L5UL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.com/dp/B0DPPLWYGX"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.com/dp/B0DQ7HD168"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.com/dp/B0DPPLWYGX?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-na.ssl-images-amazon.com/images/I/61zNj-9L5UL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.com/dp/B0DPPLWYGX"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.com/dp/B0DQ7HD168"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.com/dp/B0DQ7HD168?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-na.ssl-images-amazon.com/images/I/51e70-aZRJL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.com/dp/B0DQ7HD168"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.com/dp/B0DS2389H1"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.com/dp/B0DQ7HD168?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-na.ssl-images-amazon.com/images/I/51e70-aZRJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.com/dp/B0DQ7HD168"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.com/dp/B0DS2389H1"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.com/dp/B0DS2389H1?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-na.ssl-images-amazon.com/images/I/71RGba78P7L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.com/dp/B0DS2389H1"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.com/dp/B0DY7G7C8P"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.com/dp/B0DS2389H1?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-na.ssl-images-amazon.com/images/I/71RGba78P7L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.com/dp/B0DS2389H1"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.com/dp/B0DY7G7C8P"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.com/dp/B0DY7G7C8P?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-na.ssl-images-amazon.com/images/I/61DHdYz-K5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.com/dp/B0DY7G7C8P"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.com/dp/B0F138D56C"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.com/dp/B0DY7G7C8P?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-na.ssl-images-amazon.com/images/I/61DHdYz-K5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.com/dp/B0DY7G7C8P"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.com/dp/B0F138D56C"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.com/dp/B0F138D56C?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Tj-nSo4pL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.com/dp/B0F138D56C"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.com/dp/B0F3GYMWG5"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.com/dp/B0F138D56C?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Tj-nSo4pL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.com/dp/B0F138D56C"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.com/dp/B0F3GYMWG5"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.com/dp/B0F3GYMWG5?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.com/dp/B0F3GYMWG5"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.com/dp/B0FHHRXJ56"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.com/dp/B0F3GYMWG5?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-na.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.com/dp/B0F3GYMWG5"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.com/dp/B0FHHRXJ56"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.com/dp/B0FHHRXJ56?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-na.ssl-images-amazon.com/images/I/71f-121xiOL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.com/dp/B0FHHRXJ56"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.com/dp/B0FL781KTH"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.com/dp/B0FHHRXJ56?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-na.ssl-images-amazon.com/images/I/71f-121xiOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.com/dp/B0FHHRXJ56"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.com/dp/B0FL781KTH"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.com/dp/B0FL781KTH?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lwDHodFbL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.com/dp/B0FL781KTH"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.com/dp/B0FLJPZD5B"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.com/dp/B0FL781KTH?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lwDHodFbL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.com/dp/B0FL781KTH"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.com/dp/B0FLJPZD5B"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.com/dp/B0FLJPZD5B?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-na.ssl-images-amazon.com/images/I/71YWxGjWSZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.com/dp/B0FLJPZD5B"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.com/dp/B0FLQ68XSW"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.com/dp/B0FLJPZD5B?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-na.ssl-images-amazon.com/images/I/71YWxGjWSZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.com/dp/B0FLJPZD5B"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.com/dp/B0FLQ68XSW"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.com/dp/B0FLQ68XSW?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YxVL4HTtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.com/dp/B0FLQ68XSW"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.com/dp/B0FX9CDKGB"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.com/dp/B0FLQ68XSW?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YxVL4HTtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.com/dp/B0FLQ68XSW"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.com/dp/B0FX9CDKGB"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.com/dp/B0FX9CDKGB?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wpqOUZVdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.com/dp/B0FX9CDKGB"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.com/dp/B0G2MXVLP1"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.com/dp/B0FX9CDKGB?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wpqOUZVdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.com/dp/B0FX9CDKGB"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.com/dp/B0G2MXVLP1"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.com/dp/B0G2MXVLP1?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-na.ssl-images-amazon.com/images/I/71UEOWV8bNL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.com/dp/B0G2MXVLP1"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.com/dp/B0G2P53KJR"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.com/dp/B0G2MXVLP1?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-na.ssl-images-amazon.com/images/I/71UEOWV8bNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.com/dp/B0G2MXVLP1"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.com/dp/B0G2P53KJR"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.com/dp/B0G2P53KJR?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-na.ssl-images-amazon.com/images/I/81J1mKjTT8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.com/dp/B0G2P53KJR"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.com/dp/B0G3RT4R7C"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.com/dp/B0G2P53KJR?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-na.ssl-images-amazon.com/images/I/81J1mKjTT8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.com/dp/B0G2P53KJR"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.com/dp/B0G3RT4R7C"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.com/dp/B0G3RT4R7C?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Kv8NtfkFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.com/dp/B0G3RT4R7C"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.com/dp/B0G4W2GMRS"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.com/dp/B0G3RT4R7C?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Kv8NtfkFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.com/dp/B0G3RT4R7C"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.com/dp/B0G4W2GMRS"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.com/dp/B0G4W2GMRS?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-na.ssl-images-amazon.com/images/I/61sDpXvYzHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.com/dp/B0G4W2GMRS"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.com/dp/B0GDZBQV83"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.com/dp/B0G4W2GMRS?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-na.ssl-images-amazon.com/images/I/61sDpXvYzHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.com/dp/B0G4W2GMRS"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.com/dp/B0GDZBQV83"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.com/dp/B0GDZBQV83?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-na.ssl-images-amazon.com/images/I/51MR6wHXuGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.com/dp/B0GDZBQV83"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.com/dp/B0GH3FSR4D"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.com/dp/B0GDZBQV83?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/51MR6wHXuGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.com/dp/B0GDZBQV83"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.com/dp/B0GH3FSR4D"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.com/dp/B0GH3FSR4D?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/61U0uZOviIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.com/dp/B0GH3FSR4D"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.com/dp/B0GSKPS7BZ"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.com/dp/B0GH3FSR4D?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-na.ssl-images-amazon.com/images/I/61U0uZOviIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.com/dp/B0GH3FSR4D"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.com/dp/B0GSKPS7BZ"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.com/dp/B0GSKPS7BZ?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-na.ssl-images-amazon.com/images/I/61MFjSLQThL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.com/dp/B0GSKPS7BZ"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.com/dp/B0GSWSYTVH"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.com/dp/B0GSKPS7BZ?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/61MFjSLQThL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.com/dp/B0GSKPS7BZ"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.com/dp/B0GSWSYTVH"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.com/dp/B0GSWSYTVH?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Vj2UTHenL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.com/dp/B0GSWSYTVH"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.com/dp/B0GVJ8VWRG"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.com/dp/B0GSWSYTVH?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Vj2UTHenL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.com/dp/B0GSWSYTVH"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.com/dp/B0GVJ8VWRG"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.com/dp/B0GVJ8VWRG?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-na.ssl-images-amazon.com/images/I/61zyPjyvN0L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.com/dp/B0GVJ8VWRG"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.com/dp/B0GWPHZ5XW"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.com/dp/B0GVJ8VWRG?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-na.ssl-images-amazon.com/images/I/61zyPjyvN0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.com/dp/B0GVJ8VWRG"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.com/dp/B0GWPHZ5XW"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.com/dp/B0GWPHZ5XW?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-na.ssl-images-amazon.com/images/I/61CFmCWgPvL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.com/dp/B0GWPHZ5XW"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.com/dp/B0GXDZGMR6"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.com/dp/B0GWPHZ5XW?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/61CFmCWgPvL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.com/dp/B0GWPHZ5XW"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.com/dp/B0GXDZGMR6"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.com/dp/B0GXDZGMR6?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/51CBvrPg5DL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.com/dp/B0GXDZGMR6"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.com/dp/B0H1X526LW"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.com/dp/B0GXDZGMR6?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/51CBvrPg5DL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.com/dp/B0GXDZGMR6"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.com/dp/B0GY5Z5BT4"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.com/dp/B0H1X526LW?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Yuy5vtWFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.com/dp/B0H1X526LW"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.com/dp/B0H41F4Q7Q"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.com/dp/B0GY5Z5BT4?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-na.ssl-images-amazon.com/images/I/61QCWF0RVJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.com/dp/B0GY5Z5BT4"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.com/dp/B0H1X526LW"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.com/dp/B0H41F4Q7Q?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-na.ssl-images-amazon.com/images/I/61uSOtfOTBL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.com/dp/B0H41F4Q7Q"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.com/dp/B0H4ZTQ666"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.com/dp/B0H1X526LW?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Yuy5vtWFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.com/dp/B0H1X526LW"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.com/dp/B0H41F4Q7Q"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.com/dp/B0H4ZTQ666?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-na.ssl-images-amazon.com/images/I/6115RCOB5eL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.com/dp/B0H4ZTQ666"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.com/dp/B0H6QR43T8"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.com/dp/B0H41F4Q7Q?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/61uSOtfOTBL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.com/dp/B0H41F4Q7Q"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.com/dp/B0H4ZTQ666"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.com/dp/B0H6QR43T8?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/71sCLNoj7CL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.com/dp/B0H6QR43T8"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.com/dp/B0H7CKW7T8"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.com/dp/B0H4ZTQ666?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/6115RCOB5eL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.com/dp/B0H4ZTQ666"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.com/dp/B0H6QR43T8"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.com/dp/B0H7CKW7T8?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/61MqWVD4gLL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.com/dp/B0H7CKW7T8"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.com/dp/B0H8SR916V"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.com/dp/B0H6QR43T8?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/71sCLNoj7CL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.com/dp/B0H6QR43T8"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.com/dp/B0H7CKW7T8"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.com/dp/B0H8SR916V?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gMXLDqhAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.com/dp/B0H8SR916V"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.com/dp/B0HBRKPFZ1"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.com/dp/B0H7CKW7T8?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/61MqWVD4gLL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.com/dp/B0H7CKW7T8"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.com/dp/B0H8SR916V"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.com/dp/B0HBRKPFZ1?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/71OW-MoVElL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.com/dp/B0HBRKPFZ1"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.com/dp/B0HG12B1CH"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.com/dp/B0H8SR916V?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gMXLDqhAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.com/dp/B0H8SR916V"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.com/dp/B0HBRKPFZ1"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.com/dp/B0HG12B1CH?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Plsfn8YwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.com/dp/B0HG12B1CH"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.com/dp/B0HGM3QMZS"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.com/dp/B0HBRKPFZ1?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/71OW-MoVElL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.com/dp/B0HBRKPFZ1"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.com/dp/B0HG12B1CH"/>
-    <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.com/dp/B0HG12B1CH?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Plsfn8YwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.com/dp/B0HG12B1CH"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.com/dp/B0HGM3QMZS"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.com/dp/B0HGM3QMZS?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Sx+vwuVwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.com/dp/B0HGM3QMZS"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.com/dp/B0HGM3QMZS?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Sx+vwuVwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.com/dp/B0HGM3QMZS"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId241"/>
 </worksheet>
 </file>
 
